--- a/input26.xlsx
+++ b/input26.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Projects\lenght\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D6F5980-7709-473C-8371-63C3BB222FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85F56A14-4D2C-4320-854B-9D2D15E89719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <sheet name="5. Параметры" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="1" hidden="1">'2. Состав кабелей'!$A$2:$A$53</definedName>
+    <definedName name="ExternalData_1" localSheetId="1" hidden="1">'2. Состав кабелей'!$A$2:$A$54</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="143">
   <si>
     <t>📋  ЗАКАЗЫ НА КАБЕЛЬ</t>
   </si>
@@ -66,12 +66,6 @@
     <t>Кабельный журнал (отрезки через запятую)</t>
   </si>
   <si>
-    <t>ВВГнг(А)-LS 4х25мк(N)</t>
-  </si>
-  <si>
-    <t>ВВГнг(А)-FRHF 3х25мк(N,PE)</t>
-  </si>
-  <si>
     <t>🎨  СОСТАВ КАБЕЛЕЙ — цвета жил</t>
   </si>
   <si>
@@ -120,21 +114,12 @@
     <t>LS</t>
   </si>
   <si>
-    <t>Синяя</t>
-  </si>
-  <si>
-    <t>Желто-зеленая</t>
-  </si>
-  <si>
     <t>N=Синяя, PE=Натуральная</t>
   </si>
   <si>
     <t>мк</t>
   </si>
   <si>
-    <t>Коричневая</t>
-  </si>
-  <si>
     <t>25</t>
   </si>
   <si>
@@ -183,51 +168,9 @@
     <t>Барабан-А1</t>
   </si>
   <si>
-    <t>Барабан-А2</t>
-  </si>
-  <si>
-    <t>Барабан-А3</t>
-  </si>
-  <si>
-    <t>Барабан-А4</t>
-  </si>
-  <si>
-    <t>Барабан-А5</t>
-  </si>
-  <si>
-    <t>Барабан-А6</t>
-  </si>
-  <si>
-    <t>Барабан-АМ1</t>
-  </si>
-  <si>
-    <t>Барабан-АМ2</t>
-  </si>
-  <si>
-    <t>Барабан-АМ3</t>
-  </si>
-  <si>
-    <t>Барабан-Б1</t>
-  </si>
-  <si>
-    <t>Барабан-Б2</t>
-  </si>
-  <si>
-    <t>Барабан-Б3</t>
-  </si>
-  <si>
-    <t>Барабан-ВГ1</t>
-  </si>
-  <si>
-    <t>Барабан-ВГ2</t>
-  </si>
-  <si>
     <t>Изолированная</t>
   </si>
   <si>
-    <t>Серая</t>
-  </si>
-  <si>
     <t>Кабель</t>
   </si>
   <si>
@@ -532,6 +475,9 @@
   </si>
   <si>
     <t>Натуральный циф.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">КОСМОСИЛ-НН РэВнг(А)-LS 4х6ок(N)-1 ТУ 27.32.14-002-32408375-2022 </t>
   </si>
 </sst>
 </file>
@@ -760,6 +706,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -770,19 +728,7 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -796,6 +742,20 @@
         <top style="thin">
           <color auto="1"/>
         </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -822,20 +782,6 @@
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -860,18 +806,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{64AA3267-75F4-4929-AF3E-34A5254DCB1C}" name="Таблица2" displayName="Таблица2" ref="A2:A86" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="3" tableBorderDxfId="4">
-  <autoFilter ref="A2:A86" xr:uid="{64AA3267-75F4-4929-AF3E-34A5254DCB1C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{64AA3267-75F4-4929-AF3E-34A5254DCB1C}" name="Таблица2" displayName="Таблица2" ref="A2:A93" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2">
+  <autoFilter ref="A2:A93" xr:uid="{64AA3267-75F4-4929-AF3E-34A5254DCB1C}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{4860A363-5EF2-4852-9CAF-314B6C263730}" name="Марка кабеля"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{6FFE5DCE-31C8-4460-BEC1-10B6AF90FF6A}" name="Таблица2__2" displayName="Таблица2__2" ref="A2:A53" tableType="queryTable" totalsRowShown="0" tableBorderDxfId="1">
-  <autoFilter ref="A2:A53" xr:uid="{6FFE5DCE-31C8-4460-BEC1-10B6AF90FF6A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{6FFE5DCE-31C8-4460-BEC1-10B6AF90FF6A}" name="Таблица2__2" displayName="Таблица2__2" ref="A2:A54" tableType="queryTable" totalsRowShown="0" tableBorderDxfId="1">
+  <autoFilter ref="A2:A54" xr:uid="{6FFE5DCE-31C8-4460-BEC1-10B6AF90FF6A}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{5B4F965C-C526-4BA1-8029-17CA3DDB5D5D}" uniqueName="1" name="Марка кабеля" queryTableFieldId="1" dataDxfId="0"/>
   </tableColumns>
@@ -1164,7 +1110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F93"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="68.36328125" bestFit="1" customWidth="1"/>
@@ -1173,19 +1119,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="13" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
     </row>
     <row r="2" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="11" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -1196,53 +1142,53 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B3" s="2">
+      <c r="A3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3">
         <v>465</v>
       </c>
       <c r="C3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B4" s="3">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4">
         <v>185</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B5" s="2">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5">
         <v>1700</v>
       </c>
       <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B6" s="3">
+      <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6">
         <v>410</v>
       </c>
       <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="A7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7">
         <v>330</v>
       </c>
       <c r="C7" s="2"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="B8">
         <v>7855</v>
@@ -1250,7 +1196,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="B9">
         <v>7215</v>
@@ -1258,7 +1204,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="B10">
         <v>2710</v>
@@ -1266,7 +1212,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="B11">
         <v>4770</v>
@@ -1274,7 +1220,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="B12">
         <v>460</v>
@@ -1282,7 +1228,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="B13">
         <v>670</v>
@@ -1290,7 +1236,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="B14">
         <v>790</v>
@@ -1298,7 +1244,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="B15">
         <v>350</v>
@@ -1306,7 +1252,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="B16">
         <v>705</v>
@@ -1314,7 +1260,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="B17">
         <v>1035</v>
@@ -1322,7 +1268,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="B18">
         <v>6275</v>
@@ -1330,7 +1276,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="B19">
         <v>500</v>
@@ -1338,7 +1284,7 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="B20">
         <v>960</v>
@@ -1346,7 +1292,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="B21">
         <v>700</v>
@@ -1354,7 +1300,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="B22">
         <v>1135</v>
@@ -1362,7 +1308,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="B23">
         <v>960</v>
@@ -1370,7 +1316,7 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="B24">
         <v>325</v>
@@ -1378,7 +1324,7 @@
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="B25">
         <v>850</v>
@@ -1386,7 +1332,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="B26">
         <v>600</v>
@@ -1394,7 +1340,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="B27">
         <v>450</v>
@@ -1402,7 +1348,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="B28">
         <v>650</v>
@@ -1410,7 +1356,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="B29">
         <v>610</v>
@@ -1418,7 +1364,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="B30">
         <v>1800</v>
@@ -1426,7 +1372,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="B31">
         <v>440</v>
@@ -1434,7 +1380,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="B32">
         <v>115</v>
@@ -1442,7 +1388,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="B33">
         <v>10</v>
@@ -1450,7 +1396,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="B34">
         <v>330</v>
@@ -1458,7 +1404,7 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="B35">
         <v>620</v>
@@ -1466,7 +1412,7 @@
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="B36">
         <v>1595</v>
@@ -1474,7 +1420,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="B37">
         <v>1910</v>
@@ -1482,7 +1428,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B38">
         <v>735</v>
@@ -1490,7 +1436,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>115</v>
+        <v>96</v>
       </c>
       <c r="B39">
         <v>70</v>
@@ -1498,7 +1444,7 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="B40">
         <v>45</v>
@@ -1506,7 +1452,7 @@
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="B41">
         <v>105</v>
@@ -1514,7 +1460,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="B42">
         <v>195</v>
@@ -1522,7 +1468,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="B43">
         <v>300</v>
@@ -1530,7 +1476,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="B44">
         <v>400</v>
@@ -1538,7 +1484,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="B45">
         <v>120</v>
@@ -1546,7 +1492,7 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="B46">
         <v>208</v>
@@ -1554,7 +1500,7 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="B47">
         <v>270</v>
@@ -1562,7 +1508,7 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="B48">
         <v>210</v>
@@ -1570,7 +1516,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="B49">
         <v>80</v>
@@ -1578,7 +1524,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="B50">
         <v>60</v>
@@ -1586,7 +1532,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="B51">
         <v>320</v>
@@ -1594,7 +1540,7 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="B52">
         <v>50</v>
@@ -1602,7 +1548,7 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="B53">
         <v>180</v>
@@ -1610,7 +1556,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="B54">
         <v>240</v>
@@ -1618,7 +1564,7 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="B55">
         <v>255</v>
@@ -1626,7 +1572,7 @@
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="B56">
         <v>40</v>
@@ -1634,7 +1580,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="B57">
         <v>410</v>
@@ -1642,7 +1588,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="B58">
         <v>10</v>
@@ -1650,7 +1596,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="B59">
         <v>20</v>
@@ -1658,7 +1604,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="B60">
         <v>10</v>
@@ -1666,7 +1612,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="B61">
         <v>20</v>
@@ -1674,7 +1620,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="B62">
         <v>275</v>
@@ -1682,7 +1628,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="B63">
         <v>330</v>
@@ -1690,7 +1636,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>129</v>
+        <v>110</v>
       </c>
       <c r="B64">
         <v>780</v>
@@ -1698,7 +1644,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="B65">
         <v>424</v>
@@ -1706,7 +1652,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B66">
         <v>450</v>
@@ -1714,7 +1660,7 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="B67">
         <v>80</v>
@@ -1722,7 +1668,7 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="B68">
         <v>720</v>
@@ -1730,7 +1676,7 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="B69">
         <v>430</v>
@@ -1738,7 +1684,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="B70">
         <v>324</v>
@@ -1746,7 +1692,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="B71">
         <v>200</v>
@@ -1754,7 +1700,7 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="B72">
         <v>440</v>
@@ -1762,7 +1708,7 @@
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="B73">
         <v>100</v>
@@ -1770,7 +1716,7 @@
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="B74">
         <v>390</v>
@@ -1778,7 +1724,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="B75">
         <v>2960</v>
@@ -1786,7 +1732,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="B76">
         <v>100</v>
@@ -1794,7 +1740,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="B77">
         <v>20</v>
@@ -1802,7 +1748,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="B78">
         <v>610</v>
@@ -1810,7 +1756,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="B79">
         <v>940</v>
@@ -1818,7 +1764,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="B80">
         <v>300</v>
@@ -1826,7 +1772,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="B81">
         <v>2500</v>
@@ -1834,7 +1780,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="B82">
         <v>80</v>
@@ -1842,7 +1788,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="B83">
         <v>3000</v>
@@ -1850,7 +1796,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="B84">
         <v>125</v>
@@ -1858,7 +1804,7 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
       <c r="B85">
         <v>960</v>
@@ -1866,10 +1812,48 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="B86">
         <v>80</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>142</v>
+      </c>
+      <c r="B87">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B88">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B89">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B90">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B91">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B92">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B93">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -1887,7 +1871,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:S53"/>
+  <dimension ref="A1:S54"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="68.36328125" bestFit="1" customWidth="1"/>
@@ -1900,72 +1884,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
+      <c r="A1" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
     </row>
     <row r="2" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="Q2" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="R2" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="S2" t="s">
-        <v>154</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A3" s="16" t="s">
-        <v>101</v>
+      <c r="A3" t="s">
+        <v>82</v>
       </c>
       <c r="B3" t="str">
         <f>IFERROR(
@@ -1982,7 +1966,7 @@
 )</f>
         <v>2,5</v>
       </c>
-      <c r="C3" s="16" t="str">
+      <c r="C3" t="str">
         <f>IF(
     ISNUMBER(SEARCH("ок", Q4)),
     "ок",
@@ -2003,20 +1987,20 @@
         <v/>
       </c>
       <c r="E3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F3" t="str">
         <f>IF( R3 &gt;= 1, "Натуральный", "-" )</f>
         <v>Натуральный</v>
       </c>
       <c r="G3" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H3" t="s">
-        <v>157</v>
-      </c>
-      <c r="K3" s="17" t="s">
-        <v>25</v>
+        <v>138</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="Q3" t="str">
         <f>IFERROR(
@@ -2057,8 +2041,8 @@
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A4" s="16" t="s">
-        <v>102</v>
+      <c r="A4" t="s">
+        <v>83</v>
       </c>
       <c r="B4" t="str">
         <f t="shared" ref="B4:B53" si="0">IFERROR(
@@ -2075,7 +2059,7 @@
 )</f>
         <v>25</v>
       </c>
-      <c r="C4" s="16" t="str">
+      <c r="C4" t="str">
         <f t="shared" ref="C4:C53" si="1">IF(
     ISNUMBER(SEARCH("ок", Q5)),
     "ок",
@@ -2096,20 +2080,20 @@
         <v/>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F4" t="str">
         <f t="shared" ref="F4:F53" si="2">IF( R4 &gt;= 1, "Натуральный", "-" )</f>
         <v>Натуральный</v>
       </c>
       <c r="G4" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H4" t="s">
-        <v>157</v>
-      </c>
-      <c r="K4" s="18" t="s">
-        <v>25</v>
+        <v>138</v>
+      </c>
+      <c r="K4" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="Q4" t="str">
         <f>IFERROR(
@@ -2150,14 +2134,14 @@
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A5" s="16" t="s">
-        <v>103</v>
+      <c r="A5" t="s">
+        <v>84</v>
       </c>
       <c r="B5" t="str">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C5" s="16" t="str">
+      <c r="C5" t="str">
         <f t="shared" si="1"/>
         <v>мк</v>
       </c>
@@ -2170,20 +2154,20 @@
         <v/>
       </c>
       <c r="E5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F5" t="str">
         <f t="shared" si="2"/>
         <v>Натуральный</v>
       </c>
       <c r="G5" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H5" t="s">
-        <v>157</v>
-      </c>
-      <c r="K5" s="17" t="s">
-        <v>29</v>
+        <v>138</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>24</v>
       </c>
       <c r="Q5" t="str">
         <f>IFERROR(
@@ -2217,14 +2201,14 @@
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A6" s="16" t="s">
-        <v>104</v>
+      <c r="A6" t="s">
+        <v>85</v>
       </c>
       <c r="B6" t="str">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C6" s="16" t="str">
+      <c r="C6" t="str">
         <f t="shared" si="1"/>
         <v>мк</v>
       </c>
@@ -2237,23 +2221,23 @@
         <v/>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F6" t="str">
         <f t="shared" ref="F6:F8" si="4">IF( R6 &gt;= 1, "Натуральный", "-" )</f>
         <v>Натуральный</v>
       </c>
       <c r="H6" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I6" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J6" t="s">
-        <v>159</v>
-      </c>
-      <c r="K6" s="18" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K6" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="Q6" t="str">
         <f>IFERROR(
@@ -2287,14 +2271,14 @@
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A7" s="16" t="s">
-        <v>105</v>
+      <c r="A7" t="s">
+        <v>86</v>
       </c>
       <c r="B7" t="str">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C7" s="16" t="str">
+      <c r="C7" t="str">
         <f t="shared" si="1"/>
         <v>мк</v>
       </c>
@@ -2307,23 +2291,23 @@
         <v/>
       </c>
       <c r="E7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F7" t="str">
         <f t="shared" si="4"/>
         <v>Натуральный</v>
       </c>
       <c r="H7" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I7" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J7" t="s">
-        <v>159</v>
-      </c>
-      <c r="K7" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q7" t="str">
         <f>IFERROR(
@@ -2357,14 +2341,14 @@
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A8" s="16" t="s">
-        <v>106</v>
+      <c r="A8" t="s">
+        <v>87</v>
       </c>
       <c r="B8" t="str">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C8" s="16" t="str">
+      <c r="C8" t="str">
         <f t="shared" si="1"/>
         <v>мк</v>
       </c>
@@ -2377,23 +2361,23 @@
         <v/>
       </c>
       <c r="E8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F8" t="str">
         <f t="shared" si="4"/>
         <v>Натуральный</v>
       </c>
       <c r="H8" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I8" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J8" t="s">
-        <v>159</v>
-      </c>
-      <c r="K8" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q8" t="str">
         <f>IFERROR(
@@ -2427,14 +2411,14 @@
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A9" s="16" t="s">
-        <v>107</v>
+      <c r="A9" t="s">
+        <v>88</v>
       </c>
       <c r="B9" t="str">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C9" s="16" t="str">
+      <c r="C9" t="str">
         <f t="shared" si="1"/>
         <v>мк</v>
       </c>
@@ -2447,26 +2431,26 @@
         <v/>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F9" t="str">
         <f t="shared" si="2"/>
         <v>Натуральный</v>
       </c>
       <c r="G9" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H9" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I9" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J9" t="s">
-        <v>159</v>
-      </c>
-      <c r="K9" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K9" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q9" t="str">
         <f>IFERROR(
@@ -2500,14 +2484,14 @@
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A10" s="16" t="s">
-        <v>108</v>
+      <c r="A10" t="s">
+        <v>89</v>
       </c>
       <c r="B10" t="str">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C10" s="16" t="str">
+      <c r="C10" t="str">
         <f t="shared" si="1"/>
         <v>мк</v>
       </c>
@@ -2520,26 +2504,26 @@
         <v/>
       </c>
       <c r="E10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F10" t="str">
         <f t="shared" si="2"/>
         <v>Натуральный</v>
       </c>
       <c r="G10" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H10" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I10" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J10" t="s">
-        <v>159</v>
-      </c>
-      <c r="K10" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K10" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q10" t="str">
         <f>IFERROR(
@@ -2573,14 +2557,14 @@
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A11" s="16" t="s">
-        <v>109</v>
+      <c r="A11" t="s">
+        <v>90</v>
       </c>
       <c r="B11" t="str">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C11" s="16" t="str">
+      <c r="C11" t="str">
         <f t="shared" si="1"/>
         <v>ок</v>
       </c>
@@ -2593,26 +2577,26 @@
         <v/>
       </c>
       <c r="E11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F11" t="str">
         <f t="shared" si="2"/>
         <v>Натуральный</v>
       </c>
       <c r="G11" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H11" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I11" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J11" t="s">
-        <v>159</v>
-      </c>
-      <c r="K11" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K11" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q11" t="str">
         <f>IFERROR(
@@ -2646,14 +2630,14 @@
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A12" s="16" t="s">
-        <v>110</v>
+      <c r="A12" t="s">
+        <v>91</v>
       </c>
       <c r="B12" t="str">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C12" s="16" t="str">
+      <c r="C12" t="str">
         <f t="shared" si="1"/>
         <v>ок</v>
       </c>
@@ -2666,26 +2650,26 @@
         <v/>
       </c>
       <c r="E12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F12" t="str">
         <f t="shared" si="2"/>
         <v>Натуральный</v>
       </c>
       <c r="G12" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H12" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I12" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J12" t="s">
-        <v>159</v>
-      </c>
-      <c r="K12" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q12" t="str">
         <f>IFERROR(
@@ -2719,14 +2703,14 @@
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A13" s="16" t="s">
-        <v>111</v>
+      <c r="A13" t="s">
+        <v>92</v>
       </c>
       <c r="B13" t="str">
         <f t="shared" si="0"/>
         <v>2,5</v>
       </c>
-      <c r="C13" s="16" t="str">
+      <c r="C13" t="str">
         <f t="shared" si="1"/>
         <v>мк</v>
       </c>
@@ -2739,26 +2723,26 @@
         <v>FR</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="2"/>
         <v>Натуральный</v>
       </c>
       <c r="G13" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H13" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I13" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J13" t="s">
-        <v>159</v>
-      </c>
-      <c r="K13" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K13" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q13" t="str">
         <f>IFERROR(
@@ -2792,14 +2776,14 @@
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A14" s="16" t="s">
-        <v>112</v>
+      <c r="A14" t="s">
+        <v>93</v>
       </c>
       <c r="B14" t="str">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C14" s="16" t="str">
+      <c r="C14" t="str">
         <f t="shared" si="1"/>
         <v>мк</v>
       </c>
@@ -2812,26 +2796,26 @@
         <v>FR</v>
       </c>
       <c r="E14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F14" t="str">
         <f t="shared" si="2"/>
         <v>Натуральный</v>
       </c>
       <c r="G14" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H14" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I14" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J14" t="s">
-        <v>159</v>
-      </c>
-      <c r="K14" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K14" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q14" t="str">
         <f>IFERROR(
@@ -2865,14 +2849,14 @@
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A15" s="16" t="s">
-        <v>113</v>
+      <c r="A15" t="s">
+        <v>94</v>
       </c>
       <c r="B15" t="str">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C15" s="16" t="str">
+      <c r="C15" t="str">
         <f t="shared" si="1"/>
         <v>мк</v>
       </c>
@@ -2885,26 +2869,26 @@
         <v>FR</v>
       </c>
       <c r="E15" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F15" t="str">
         <f t="shared" si="2"/>
         <v>Натуральный</v>
       </c>
       <c r="G15" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H15" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I15" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J15" t="s">
-        <v>159</v>
-      </c>
-      <c r="K15" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K15" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q15" t="str">
         <f>IFERROR(
@@ -2938,14 +2922,14 @@
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A16" s="16" t="s">
-        <v>114</v>
+      <c r="A16" t="s">
+        <v>95</v>
       </c>
       <c r="B16" t="str">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C16" s="16" t="str">
+      <c r="C16" t="str">
         <f t="shared" si="1"/>
         <v>ок</v>
       </c>
@@ -2958,26 +2942,26 @@
         <v>FR</v>
       </c>
       <c r="E16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F16" t="str">
         <f t="shared" si="2"/>
         <v>Натуральный</v>
       </c>
       <c r="G16" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H16" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I16" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J16" t="s">
-        <v>159</v>
-      </c>
-      <c r="K16" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K16" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q16" t="str">
         <f>IFERROR(
@@ -3011,14 +2995,14 @@
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A17" s="16" t="s">
-        <v>115</v>
+      <c r="A17" t="s">
+        <v>96</v>
       </c>
       <c r="B17" t="str">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C17" s="16" t="str">
+      <c r="C17" t="str">
         <f t="shared" si="1"/>
         <v>ок</v>
       </c>
@@ -3031,26 +3015,26 @@
         <v/>
       </c>
       <c r="E17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F17" t="str">
         <f t="shared" si="2"/>
         <v>Натуральный</v>
       </c>
       <c r="G17" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H17" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I17" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J17" t="s">
-        <v>159</v>
-      </c>
-      <c r="K17" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K17" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q17" t="str">
         <f>IFERROR(
@@ -3084,14 +3068,14 @@
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A18" s="16" t="s">
-        <v>116</v>
+      <c r="A18" t="s">
+        <v>97</v>
       </c>
       <c r="B18" t="str">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C18" s="16" t="str">
+      <c r="C18" t="str">
         <f t="shared" si="1"/>
         <v>ок</v>
       </c>
@@ -3104,26 +3088,26 @@
         <v/>
       </c>
       <c r="E18" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F18" t="str">
         <f t="shared" si="2"/>
         <v>Натуральный</v>
       </c>
       <c r="G18" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H18" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I18" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J18" t="s">
-        <v>159</v>
-      </c>
-      <c r="K18" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K18" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q18" t="str">
         <f>IFERROR(
@@ -3157,14 +3141,14 @@
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A19" s="16" t="s">
-        <v>117</v>
+      <c r="A19" t="s">
+        <v>98</v>
       </c>
       <c r="B19" t="str">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="16" t="str">
+      <c r="C19" t="str">
         <f t="shared" si="1"/>
         <v>мк</v>
       </c>
@@ -3177,26 +3161,26 @@
         <v/>
       </c>
       <c r="E19" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F19" t="str">
         <f t="shared" si="2"/>
         <v>Натуральный</v>
       </c>
       <c r="G19" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H19" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I19" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J19" t="s">
-        <v>159</v>
-      </c>
-      <c r="K19" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K19" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q19" t="str">
         <f>IFERROR(
@@ -3230,14 +3214,14 @@
       </c>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A20" s="16" t="s">
-        <v>118</v>
+      <c r="A20" t="s">
+        <v>99</v>
       </c>
       <c r="B20" t="str">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C20" s="16" t="str">
+      <c r="C20" t="str">
         <f t="shared" si="1"/>
         <v>ок</v>
       </c>
@@ -3250,26 +3234,26 @@
         <v/>
       </c>
       <c r="E20" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F20" t="str">
         <f t="shared" si="2"/>
         <v>Натуральный</v>
       </c>
       <c r="G20" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H20" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I20" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J20" t="s">
-        <v>159</v>
-      </c>
-      <c r="K20" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K20" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q20" t="str">
         <f>IFERROR(
@@ -3303,14 +3287,14 @@
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A21" s="16" t="s">
-        <v>119</v>
+      <c r="A21" t="s">
+        <v>100</v>
       </c>
       <c r="B21" t="str">
         <f t="shared" si="0"/>
         <v>2,5</v>
       </c>
-      <c r="C21" s="16" t="str">
+      <c r="C21" t="str">
         <f t="shared" si="1"/>
         <v>мк</v>
       </c>
@@ -3323,26 +3307,26 @@
         <v/>
       </c>
       <c r="E21" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F21" t="str">
         <f t="shared" si="2"/>
         <v>Натуральный</v>
       </c>
       <c r="G21" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H21" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I21" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J21" t="s">
-        <v>159</v>
-      </c>
-      <c r="K21" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K21" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q21" t="str">
         <f>IFERROR(
@@ -3376,14 +3360,14 @@
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A22" s="16" t="s">
-        <v>120</v>
+      <c r="A22" t="s">
+        <v>101</v>
       </c>
       <c r="B22" t="str">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C22" s="16" t="str">
+      <c r="C22" t="str">
         <f t="shared" si="1"/>
         <v>ок-к</v>
       </c>
@@ -3396,26 +3380,26 @@
         <v/>
       </c>
       <c r="E22" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F22" t="str">
         <f t="shared" si="2"/>
         <v>Натуральный</v>
       </c>
       <c r="G22" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H22" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I22" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J22" t="s">
-        <v>159</v>
-      </c>
-      <c r="K22" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K22" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q22" t="str">
         <f>IFERROR(
@@ -3449,14 +3433,14 @@
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A23" s="16" t="s">
-        <v>121</v>
+      <c r="A23" t="s">
+        <v>102</v>
       </c>
       <c r="B23" t="str">
         <f t="shared" si="0"/>
         <v>1,5</v>
       </c>
-      <c r="C23" s="16" t="str">
+      <c r="C23" t="str">
         <f t="shared" si="1"/>
         <v>ок-к</v>
       </c>
@@ -3469,13 +3453,13 @@
         <v/>
       </c>
       <c r="E23" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F23" t="s">
-        <v>160</v>
-      </c>
-      <c r="K23" s="17" t="s">
-        <v>30</v>
+        <v>141</v>
+      </c>
+      <c r="K23" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q23" t="str">
         <f>IFERROR(
@@ -3509,14 +3493,14 @@
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A24" s="16" t="s">
-        <v>122</v>
+      <c r="A24" t="s">
+        <v>103</v>
       </c>
       <c r="B24" t="str">
         <f t="shared" si="0"/>
         <v>1,5</v>
       </c>
-      <c r="C24" s="16" t="str">
+      <c r="C24" t="str">
         <f t="shared" si="1"/>
         <v>ок-к</v>
       </c>
@@ -3529,13 +3513,13 @@
         <v/>
       </c>
       <c r="E24" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F24" t="s">
-        <v>160</v>
-      </c>
-      <c r="K24" s="17" t="s">
-        <v>30</v>
+        <v>141</v>
+      </c>
+      <c r="K24" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q24" t="str">
         <f>IFERROR(
@@ -3569,14 +3553,14 @@
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A25" s="16" t="s">
-        <v>123</v>
+      <c r="A25" t="s">
+        <v>104</v>
       </c>
       <c r="B25" t="str">
         <f t="shared" si="0"/>
         <v>1,5</v>
       </c>
-      <c r="C25" s="16" t="str">
+      <c r="C25" t="str">
         <f t="shared" si="1"/>
         <v>ок-к</v>
       </c>
@@ -3589,26 +3573,26 @@
         <v/>
       </c>
       <c r="E25" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F25" t="str">
         <f t="shared" si="2"/>
         <v>Натуральный</v>
       </c>
       <c r="G25" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H25" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I25" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J25" t="s">
-        <v>159</v>
-      </c>
-      <c r="K25" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K25" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q25" t="str">
         <f>IFERROR(
@@ -3642,14 +3626,14 @@
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A26" s="16" t="s">
-        <v>124</v>
+      <c r="A26" t="s">
+        <v>105</v>
       </c>
       <c r="B26" t="str">
         <f t="shared" si="0"/>
         <v>2,5</v>
       </c>
-      <c r="C26" s="16" t="str">
+      <c r="C26" t="str">
         <f t="shared" si="1"/>
         <v>ок</v>
       </c>
@@ -3662,26 +3646,26 @@
         <v/>
       </c>
       <c r="E26" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F26" t="str">
         <f t="shared" si="2"/>
         <v>Натуральный</v>
       </c>
       <c r="G26" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H26" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I26" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J26" t="s">
-        <v>159</v>
-      </c>
-      <c r="K26" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K26" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q26" t="str">
         <f>IFERROR(
@@ -3715,14 +3699,14 @@
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A27" s="16" t="s">
-        <v>125</v>
+      <c r="A27" t="s">
+        <v>106</v>
       </c>
       <c r="B27" t="str">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C27" s="16" t="str">
+      <c r="C27" t="str">
         <f t="shared" si="1"/>
         <v>ок</v>
       </c>
@@ -3735,17 +3719,17 @@
         <v/>
       </c>
       <c r="E27" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="F27" t="str">
         <f t="shared" si="2"/>
         <v>Натуральный</v>
       </c>
       <c r="H27" t="s">
-        <v>157</v>
-      </c>
-      <c r="K27" s="17" t="s">
-        <v>30</v>
+        <v>138</v>
+      </c>
+      <c r="K27" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q27" t="str">
         <f>IFERROR(
@@ -3779,14 +3763,14 @@
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A28" s="16" t="s">
-        <v>126</v>
+      <c r="A28" t="s">
+        <v>107</v>
       </c>
       <c r="B28" t="str">
         <f t="shared" si="0"/>
         <v>2,5</v>
       </c>
-      <c r="C28" s="16" t="str">
+      <c r="C28" t="str">
         <f t="shared" si="1"/>
         <v>мк</v>
       </c>
@@ -3799,23 +3783,23 @@
         <v/>
       </c>
       <c r="E28" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="F28" t="str">
         <f t="shared" ref="F28:F41" si="5">IF( R28 &gt;= 1, "Натуральный", "-" )</f>
         <v>Натуральный</v>
       </c>
       <c r="H28" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I28" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J28" t="s">
-        <v>159</v>
-      </c>
-      <c r="K28" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K28" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q28" t="str">
         <f>IFERROR(
@@ -3849,14 +3833,14 @@
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A29" s="16" t="s">
-        <v>127</v>
+      <c r="A29" t="s">
+        <v>108</v>
       </c>
       <c r="B29" t="str">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C29" s="16" t="str">
+      <c r="C29" t="str">
         <f t="shared" si="1"/>
         <v>мк</v>
       </c>
@@ -3869,23 +3853,23 @@
         <v/>
       </c>
       <c r="E29" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="F29" t="str">
         <f t="shared" si="5"/>
         <v>Натуральный</v>
       </c>
       <c r="H29" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I29" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J29" t="s">
-        <v>159</v>
-      </c>
-      <c r="K29" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K29" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q29" t="str">
         <f>IFERROR(
@@ -3919,14 +3903,14 @@
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A30" s="16" t="s">
-        <v>128</v>
+      <c r="A30" t="s">
+        <v>109</v>
       </c>
       <c r="B30" t="str">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C30" s="16" t="str">
+      <c r="C30" t="str">
         <f t="shared" si="1"/>
         <v>ок</v>
       </c>
@@ -3939,23 +3923,23 @@
         <v/>
       </c>
       <c r="E30" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="F30" t="str">
         <f t="shared" si="5"/>
         <v>Натуральный</v>
       </c>
       <c r="H30" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I30" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J30" t="s">
-        <v>159</v>
-      </c>
-      <c r="K30" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K30" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q30" t="str">
         <f>IFERROR(
@@ -3989,14 +3973,14 @@
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A31" s="16" t="s">
-        <v>129</v>
+      <c r="A31" t="s">
+        <v>110</v>
       </c>
       <c r="B31" t="str">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C31" s="16" t="str">
+      <c r="C31" t="str">
         <f t="shared" si="1"/>
         <v>ок</v>
       </c>
@@ -4009,23 +3993,23 @@
         <v/>
       </c>
       <c r="E31" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="F31" t="str">
         <f t="shared" si="5"/>
         <v>Натуральный</v>
       </c>
       <c r="H31" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I31" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J31" t="s">
-        <v>159</v>
-      </c>
-      <c r="K31" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K31" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q31" t="str">
         <f>IFERROR(
@@ -4059,14 +4043,14 @@
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A32" s="16" t="s">
-        <v>130</v>
+      <c r="A32" t="s">
+        <v>111</v>
       </c>
       <c r="B32" t="str">
         <f t="shared" si="0"/>
         <v>2,5</v>
       </c>
-      <c r="C32" s="16" t="str">
+      <c r="C32" t="str">
         <f t="shared" si="1"/>
         <v>мк</v>
       </c>
@@ -4079,23 +4063,23 @@
         <v/>
       </c>
       <c r="E32" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F32" t="str">
         <f t="shared" si="5"/>
         <v>Натуральный</v>
       </c>
       <c r="H32" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I32" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J32" t="s">
-        <v>159</v>
-      </c>
-      <c r="K32" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K32" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q32" t="str">
         <f>IFERROR(
@@ -4129,14 +4113,14 @@
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A33" s="16" t="s">
-        <v>131</v>
+      <c r="A33" t="s">
+        <v>112</v>
       </c>
       <c r="B33" t="str">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C33" s="16" t="str">
+      <c r="C33" t="str">
         <f t="shared" si="1"/>
         <v>ок</v>
       </c>
@@ -4149,23 +4133,23 @@
         <v/>
       </c>
       <c r="E33" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F33" t="str">
         <f t="shared" si="5"/>
         <v>Натуральный</v>
       </c>
       <c r="H33" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I33" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J33" t="s">
-        <v>159</v>
-      </c>
-      <c r="K33" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K33" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q33" t="str">
         <f>IFERROR(
@@ -4199,14 +4183,14 @@
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A34" s="16" t="s">
-        <v>132</v>
+      <c r="A34" t="s">
+        <v>113</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C34" s="16" t="str">
+      <c r="C34" t="str">
         <f t="shared" si="1"/>
         <v>ок</v>
       </c>
@@ -4219,23 +4203,23 @@
         <v/>
       </c>
       <c r="E34" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F34" t="str">
         <f t="shared" si="5"/>
         <v>Натуральный</v>
       </c>
       <c r="H34" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I34" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J34" t="s">
-        <v>159</v>
-      </c>
-      <c r="K34" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K34" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q34" t="str">
         <f>IFERROR(
@@ -4269,14 +4253,14 @@
       </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A35" s="16" t="s">
-        <v>133</v>
+      <c r="A35" t="s">
+        <v>114</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C35" s="16" t="str">
+      <c r="C35" t="str">
         <f t="shared" si="1"/>
         <v>мк</v>
       </c>
@@ -4289,23 +4273,23 @@
         <v/>
       </c>
       <c r="E35" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F35" t="str">
         <f t="shared" si="5"/>
         <v>Натуральный</v>
       </c>
       <c r="H35" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I35" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J35" t="s">
-        <v>159</v>
-      </c>
-      <c r="K35" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K35" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q35" t="str">
         <f>IFERROR(
@@ -4339,14 +4323,14 @@
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A36" s="16" t="s">
-        <v>134</v>
+      <c r="A36" t="s">
+        <v>115</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C36" s="16" t="str">
+      <c r="C36" t="str">
         <f t="shared" si="1"/>
         <v>ок</v>
       </c>
@@ -4359,26 +4343,26 @@
         <v/>
       </c>
       <c r="E36" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F36" t="str">
         <f t="shared" si="5"/>
         <v>Натуральный</v>
       </c>
       <c r="G36" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H36" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I36" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J36" t="s">
-        <v>159</v>
-      </c>
-      <c r="K36" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K36" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q36" t="str">
         <f>IFERROR(
@@ -4412,14 +4396,14 @@
       </c>
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A37" s="16" t="s">
-        <v>135</v>
+      <c r="A37" t="s">
+        <v>116</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="0"/>
         <v>2,5</v>
       </c>
-      <c r="C37" s="16" t="str">
+      <c r="C37" t="str">
         <f t="shared" si="1"/>
         <v>мк</v>
       </c>
@@ -4432,26 +4416,26 @@
         <v/>
       </c>
       <c r="E37" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F37" t="str">
         <f t="shared" si="5"/>
         <v>Натуральный</v>
       </c>
       <c r="G37" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H37" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I37" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J37" t="s">
-        <v>159</v>
-      </c>
-      <c r="K37" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K37" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q37" t="str">
         <f>IFERROR(
@@ -4485,14 +4469,14 @@
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A38" s="16" t="s">
-        <v>136</v>
+      <c r="A38" t="s">
+        <v>117</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="C38" s="16" t="str">
+      <c r="C38" t="str">
         <f t="shared" si="1"/>
         <v>ок</v>
       </c>
@@ -4505,26 +4489,26 @@
         <v/>
       </c>
       <c r="E38" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F38" t="str">
         <f t="shared" si="5"/>
         <v>Натуральный</v>
       </c>
       <c r="G38" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H38" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I38" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J38" t="s">
-        <v>159</v>
-      </c>
-      <c r="K38" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K38" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q38" t="str">
         <f>IFERROR(
@@ -4558,14 +4542,14 @@
       </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A39" s="16" t="s">
-        <v>137</v>
+      <c r="A39" t="s">
+        <v>118</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C39" s="16" t="str">
+      <c r="C39" t="str">
         <f t="shared" si="1"/>
         <v>ок</v>
       </c>
@@ -4578,23 +4562,23 @@
         <v/>
       </c>
       <c r="E39" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F39" t="str">
         <f t="shared" si="5"/>
         <v>Натуральный</v>
       </c>
       <c r="H39" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I39" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J39" t="s">
-        <v>159</v>
-      </c>
-      <c r="K39" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K39" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q39" t="str">
         <f>IFERROR(
@@ -4628,14 +4612,14 @@
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A40" s="16" t="s">
-        <v>138</v>
+      <c r="A40" t="s">
+        <v>119</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="0"/>
         <v>2,5</v>
       </c>
-      <c r="C40" s="16" t="str">
+      <c r="C40" t="str">
         <f t="shared" si="1"/>
         <v>ок</v>
       </c>
@@ -4648,23 +4632,23 @@
         <v/>
       </c>
       <c r="E40" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F40" t="str">
         <f t="shared" si="5"/>
         <v>Натуральный</v>
       </c>
       <c r="H40" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I40" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J40" t="s">
-        <v>159</v>
-      </c>
-      <c r="K40" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K40" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q40" t="str">
         <f>IFERROR(
@@ -4698,14 +4682,14 @@
       </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A41" s="16" t="s">
-        <v>139</v>
+      <c r="A41" t="s">
+        <v>120</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="0"/>
         <v>2,5</v>
       </c>
-      <c r="C41" s="16" t="str">
+      <c r="C41" t="str">
         <f t="shared" si="1"/>
         <v>ок-к</v>
       </c>
@@ -4718,23 +4702,23 @@
         <v/>
       </c>
       <c r="E41" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F41" t="str">
         <f t="shared" si="5"/>
         <v>Натуральный</v>
       </c>
       <c r="H41" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I41" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J41" t="s">
-        <v>159</v>
-      </c>
-      <c r="K41" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K41" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q41" t="str">
         <f>IFERROR(
@@ -4768,14 +4752,14 @@
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A42" s="16" t="s">
-        <v>140</v>
+      <c r="A42" t="s">
+        <v>121</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="0"/>
         <v>2,5</v>
       </c>
-      <c r="C42" s="16" t="str">
+      <c r="C42" t="str">
         <f t="shared" si="1"/>
         <v>ок-к</v>
       </c>
@@ -4788,20 +4772,20 @@
         <v/>
       </c>
       <c r="E42" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F42" t="str">
         <f t="shared" si="2"/>
         <v>Натуральный</v>
       </c>
       <c r="G42" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H42" t="s">
-        <v>157</v>
-      </c>
-      <c r="K42" s="17" t="s">
-        <v>30</v>
+        <v>138</v>
+      </c>
+      <c r="K42" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q42" t="str">
         <f>IFERROR(
@@ -4835,14 +4819,14 @@
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A43" s="16" t="s">
-        <v>141</v>
+      <c r="A43" t="s">
+        <v>122</v>
       </c>
       <c r="B43" t="str">
         <f t="shared" si="0"/>
         <v>1,5</v>
       </c>
-      <c r="C43" s="16" t="str">
+      <c r="C43" t="str">
         <f t="shared" si="1"/>
         <v>ок-к</v>
       </c>
@@ -4855,13 +4839,13 @@
         <v/>
       </c>
       <c r="E43" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F43" t="s">
-        <v>160</v>
-      </c>
-      <c r="K43" s="17" t="s">
-        <v>30</v>
+        <v>141</v>
+      </c>
+      <c r="K43" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q43" t="str">
         <f>IFERROR(
@@ -4895,14 +4879,14 @@
       </c>
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A44" s="16" t="s">
-        <v>142</v>
+      <c r="A44" t="s">
+        <v>123</v>
       </c>
       <c r="B44" t="str">
         <f t="shared" si="0"/>
         <v>1,5</v>
       </c>
-      <c r="C44" s="16" t="str">
+      <c r="C44" t="str">
         <f t="shared" si="1"/>
         <v>ок-к</v>
       </c>
@@ -4915,13 +4899,13 @@
         <v/>
       </c>
       <c r="E44" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F44" t="s">
-        <v>160</v>
-      </c>
-      <c r="K44" s="17" t="s">
-        <v>30</v>
+        <v>141</v>
+      </c>
+      <c r="K44" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q44" t="str">
         <f>IFERROR(
@@ -4955,14 +4939,14 @@
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A45" s="16" t="s">
-        <v>143</v>
+      <c r="A45" t="s">
+        <v>124</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="0"/>
         <v>1,5</v>
       </c>
-      <c r="C45" s="16" t="str">
+      <c r="C45" t="str">
         <f t="shared" si="1"/>
         <v>ок-к</v>
       </c>
@@ -4975,13 +4959,13 @@
         <v/>
       </c>
       <c r="E45" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F45" t="s">
-        <v>160</v>
-      </c>
-      <c r="K45" s="17" t="s">
-        <v>30</v>
+        <v>141</v>
+      </c>
+      <c r="K45" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q45" t="str">
         <f>IFERROR(
@@ -5015,14 +4999,14 @@
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A46" s="16" t="s">
-        <v>144</v>
+      <c r="A46" t="s">
+        <v>125</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="0"/>
         <v>1,5</v>
       </c>
-      <c r="C46" s="16" t="str">
+      <c r="C46" t="str">
         <f t="shared" si="1"/>
         <v>ок-к</v>
       </c>
@@ -5035,13 +5019,13 @@
         <v/>
       </c>
       <c r="E46" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F46" t="s">
-        <v>160</v>
-      </c>
-      <c r="K46" s="17" t="s">
-        <v>30</v>
+        <v>141</v>
+      </c>
+      <c r="K46" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q46" t="str">
         <f>IFERROR(
@@ -5075,14 +5059,14 @@
       </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A47" s="16" t="s">
-        <v>145</v>
+      <c r="A47" t="s">
+        <v>126</v>
       </c>
       <c r="B47" t="str">
         <f t="shared" si="0"/>
         <v>2,5</v>
       </c>
-      <c r="C47" s="16" t="str">
+      <c r="C47" t="str">
         <f t="shared" si="1"/>
         <v>ок-к</v>
       </c>
@@ -5095,13 +5079,13 @@
         <v/>
       </c>
       <c r="E47" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="F47" t="s">
-        <v>160</v>
-      </c>
-      <c r="K47" s="17" t="s">
-        <v>30</v>
+        <v>141</v>
+      </c>
+      <c r="K47" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q47" t="str">
         <f>IFERROR(
@@ -5135,14 +5119,14 @@
       </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A48" s="16" t="s">
-        <v>146</v>
+      <c r="A48" t="s">
+        <v>127</v>
       </c>
       <c r="B48" t="str">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C48" s="16" t="str">
+      <c r="C48" t="str">
         <f t="shared" si="1"/>
         <v>ок-к</v>
       </c>
@@ -5155,13 +5139,13 @@
         <v/>
       </c>
       <c r="E48" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="F48" t="s">
-        <v>160</v>
-      </c>
-      <c r="K48" s="17" t="s">
-        <v>30</v>
+        <v>141</v>
+      </c>
+      <c r="K48" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q48" t="str">
         <f>IFERROR(
@@ -5195,14 +5179,14 @@
       </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A49" s="16" t="s">
-        <v>147</v>
+      <c r="A49" t="s">
+        <v>128</v>
       </c>
       <c r="B49" t="str">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C49" s="16" t="str">
+      <c r="C49" t="str">
         <f t="shared" si="1"/>
         <v>ок-к</v>
       </c>
@@ -5215,13 +5199,13 @@
         <v/>
       </c>
       <c r="E49" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="F49" t="s">
-        <v>160</v>
-      </c>
-      <c r="K49" s="17" t="s">
-        <v>30</v>
+        <v>141</v>
+      </c>
+      <c r="K49" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q49" t="str">
         <f>IFERROR(
@@ -5255,14 +5239,14 @@
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A50" s="16" t="s">
-        <v>148</v>
+      <c r="A50" t="s">
+        <v>129</v>
       </c>
       <c r="B50" t="str">
         <f t="shared" si="0"/>
         <v>1,5</v>
       </c>
-      <c r="C50" s="16" t="str">
+      <c r="C50" t="str">
         <f t="shared" si="1"/>
         <v>мк</v>
       </c>
@@ -5275,20 +5259,20 @@
         <v/>
       </c>
       <c r="E50" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="F50" t="str">
         <f t="shared" si="2"/>
         <v>Натуральный</v>
       </c>
       <c r="G50" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H50" t="s">
-        <v>157</v>
-      </c>
-      <c r="K50" s="17" t="s">
-        <v>30</v>
+        <v>138</v>
+      </c>
+      <c r="K50" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q50" t="str">
         <f>IFERROR(
@@ -5322,14 +5306,14 @@
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A51" s="16" t="s">
-        <v>149</v>
+      <c r="A51" t="s">
+        <v>130</v>
       </c>
       <c r="B51" t="str">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C51" s="16" t="str">
+      <c r="C51" t="str">
         <f t="shared" si="1"/>
         <v>ок</v>
       </c>
@@ -5342,20 +5326,20 @@
         <v/>
       </c>
       <c r="E51" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="F51" t="str">
         <f t="shared" si="2"/>
         <v>Натуральный</v>
       </c>
       <c r="G51" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H51" t="s">
-        <v>157</v>
-      </c>
-      <c r="K51" s="17" t="s">
-        <v>30</v>
+        <v>138</v>
+      </c>
+      <c r="K51" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q51" t="str">
         <f>IFERROR(
@@ -5389,14 +5373,14 @@
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A52" s="16" t="s">
-        <v>150</v>
+      <c r="A52" t="s">
+        <v>131</v>
       </c>
       <c r="B52" t="str">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C52" s="16" t="str">
+      <c r="C52" t="str">
         <f t="shared" si="1"/>
         <v>мк</v>
       </c>
@@ -5409,20 +5393,20 @@
         <v/>
       </c>
       <c r="E52" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="F52" t="str">
         <f t="shared" si="2"/>
         <v>Натуральный</v>
       </c>
       <c r="G52" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="H52" t="s">
-        <v>157</v>
-      </c>
-      <c r="K52" s="17" t="s">
-        <v>30</v>
+        <v>138</v>
+      </c>
+      <c r="K52" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q52" t="str">
         <f>IFERROR(
@@ -5456,14 +5440,14 @@
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A53" s="16" t="s">
-        <v>151</v>
+      <c r="A53" t="s">
+        <v>132</v>
       </c>
       <c r="B53" t="str">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C53" s="16" t="str">
+      <c r="C53" t="str">
         <f t="shared" si="1"/>
         <v>ок-к</v>
       </c>
@@ -5476,23 +5460,23 @@
         <v/>
       </c>
       <c r="E53" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="F53" t="str">
         <f t="shared" si="2"/>
         <v>Натуральный</v>
       </c>
       <c r="H53" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I53" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="J53" t="s">
-        <v>159</v>
-      </c>
-      <c r="K53" s="17" t="s">
-        <v>30</v>
+        <v>140</v>
+      </c>
+      <c r="K53" s="12" t="s">
+        <v>25</v>
       </c>
       <c r="Q53" t="str">
         <f>IFERROR(
@@ -5525,11 +5509,42 @@
         <v>N</v>
       </c>
     </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A54" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="B54">
+        <v>6</v>
+      </c>
+      <c r="C54" t="s">
+        <v>18</v>
+      </c>
+      <c r="E54" t="s">
+        <v>20</v>
+      </c>
+      <c r="F54" t="str">
+        <f t="shared" ref="F54" si="6">IF( R54 &gt;= 1, "Натуральный", "-" )</f>
+        <v>-</v>
+      </c>
+      <c r="H54" t="s">
+        <v>138</v>
+      </c>
+      <c r="I54" t="s">
+        <v>139</v>
+      </c>
+      <c r="J54" t="s">
+        <v>140</v>
+      </c>
+      <c r="K54" s="12" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="K1:N1"/>
     <mergeCell ref="A1:J1"/>
   </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -5554,51 +5569,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
+      <c r="A1" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
     </row>
     <row r="2" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -5606,28 +5621,28 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="4">
+        <v>25</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="F3" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H3" s="4">
-        <v>9000</v>
+        <v>500000</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -5635,403 +5650,339 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="F4" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H4" s="4">
-        <v>9000</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>44</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="F5" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="4">
-        <v>9000</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>45</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="F6" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="4">
-        <v>2000</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="F7" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="4">
-        <v>1000</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>47</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="F8" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="4">
-        <v>400</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>48</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="F9" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="4">
-        <v>9000</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>49</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="F10" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H10" s="4">
-        <v>9000</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>50</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="F11" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="4">
-        <v>9000</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>51</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H12" s="4">
-        <v>8000</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>52</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" s="4">
-        <v>8000</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>53</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14" s="4">
-        <v>4000</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>54</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H15" s="4">
-        <v>8000</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>55</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16" s="4">
-        <v>8000</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>56</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>15</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H17" s="5">
-        <v>6000</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
       <c r="I17" s="5"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
@@ -6039,26 +5990,14 @@
         <v>16</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H18" s="5">
-        <v>12000</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
       <c r="I18" s="5"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
@@ -6066,26 +6005,14 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H19" s="5">
-        <v>500</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
       <c r="I19" s="5"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
@@ -6093,26 +6020,14 @@
         <v>18</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="H20" s="5">
-        <v>2000</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
       <c r="I20" s="5"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
@@ -6120,26 +6035,22 @@
         <v>19</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="H21" s="6">
-        <v>300</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
       <c r="I21" s="6"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
@@ -6147,37 +6058,33 @@
         <v>20</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="H22" s="6">
-        <v>500</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
       <c r="I22" s="6"/>
     </row>
     <row r="24" spans="1:9" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -6201,64 +6108,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="A1" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
     </row>
     <row r="3" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+      <c r="A3" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
     </row>
     <row r="4" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
+      <c r="A4" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
     </row>
     <row r="5" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C6" s="2">
         <v>2500</v>
@@ -6272,10 +6179,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C7" s="3">
         <v>2500</v>
@@ -6289,10 +6196,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C8" s="2">
         <v>1000</v>
@@ -6306,10 +6213,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C9" s="3">
         <v>1000</v>
@@ -6322,47 +6229,47 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="B12" s="12"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
+      <c r="A12" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
     </row>
     <row r="13" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
+      <c r="A13" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
     </row>
     <row r="14" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="19" t="s">
-        <v>101</v>
+      <c r="A15" s="14" t="s">
+        <v>82</v>
       </c>
       <c r="B15" s="2">
         <v>600</v>
@@ -6375,8 +6282,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="20" t="s">
-        <v>102</v>
+      <c r="A16" s="15" t="s">
+        <v>83</v>
       </c>
       <c r="B16" s="3">
         <v>450</v>
@@ -6389,8 +6296,8 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="19" t="s">
-        <v>103</v>
+      <c r="A17" s="14" t="s">
+        <v>84</v>
       </c>
       <c r="B17" s="2">
         <v>300</v>
@@ -6403,8 +6310,8 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="20" t="s">
-        <v>104</v>
+      <c r="A18" s="15" t="s">
+        <v>85</v>
       </c>
       <c r="B18" s="3">
         <v>350</v>
@@ -6417,8 +6324,8 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="19" t="s">
-        <v>105</v>
+      <c r="A19" s="14" t="s">
+        <v>86</v>
       </c>
       <c r="B19" s="2">
         <v>300</v>
@@ -6431,8 +6338,8 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="20" t="s">
-        <v>106</v>
+      <c r="A20" s="15" t="s">
+        <v>87</v>
       </c>
       <c r="B20" s="2">
         <v>300</v>
@@ -6445,8 +6352,8 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="19" t="s">
-        <v>107</v>
+      <c r="A21" s="14" t="s">
+        <v>88</v>
       </c>
       <c r="B21" s="2">
         <v>300</v>
@@ -6459,8 +6366,8 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="20" t="s">
-        <v>108</v>
+      <c r="A22" s="15" t="s">
+        <v>89</v>
       </c>
       <c r="B22" s="2">
         <v>300</v>
@@ -6473,8 +6380,8 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="19" t="s">
-        <v>109</v>
+      <c r="A23" s="14" t="s">
+        <v>90</v>
       </c>
       <c r="B23" s="2">
         <v>300</v>
@@ -6487,8 +6394,8 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="20" t="s">
-        <v>110</v>
+      <c r="A24" s="15" t="s">
+        <v>91</v>
       </c>
       <c r="B24" s="2">
         <v>300</v>
@@ -6501,8 +6408,8 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="19" t="s">
-        <v>111</v>
+      <c r="A25" s="14" t="s">
+        <v>92</v>
       </c>
       <c r="B25" s="2">
         <v>300</v>
@@ -6515,8 +6422,8 @@
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="20" t="s">
-        <v>112</v>
+      <c r="A26" s="15" t="s">
+        <v>93</v>
       </c>
       <c r="B26" s="2">
         <v>300</v>
@@ -6529,8 +6436,8 @@
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="19" t="s">
-        <v>113</v>
+      <c r="A27" s="14" t="s">
+        <v>94</v>
       </c>
       <c r="B27" s="2">
         <v>300</v>
@@ -6543,8 +6450,8 @@
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="20" t="s">
-        <v>114</v>
+      <c r="A28" s="15" t="s">
+        <v>95</v>
       </c>
       <c r="B28" s="2">
         <v>300</v>
@@ -6557,8 +6464,8 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="19" t="s">
-        <v>115</v>
+      <c r="A29" s="14" t="s">
+        <v>96</v>
       </c>
       <c r="B29" s="2">
         <v>300</v>
@@ -6571,8 +6478,8 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="20" t="s">
-        <v>116</v>
+      <c r="A30" s="15" t="s">
+        <v>97</v>
       </c>
       <c r="B30" s="2">
         <v>300</v>
@@ -6585,8 +6492,8 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="19" t="s">
-        <v>117</v>
+      <c r="A31" s="14" t="s">
+        <v>98</v>
       </c>
       <c r="B31" s="2">
         <v>300</v>
@@ -6599,8 +6506,8 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="20" t="s">
-        <v>118</v>
+      <c r="A32" s="15" t="s">
+        <v>99</v>
       </c>
       <c r="B32" s="2">
         <v>300</v>
@@ -6613,8 +6520,8 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="19" t="s">
-        <v>119</v>
+      <c r="A33" s="14" t="s">
+        <v>100</v>
       </c>
       <c r="B33" s="2">
         <v>300</v>
@@ -6627,8 +6534,8 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="20" t="s">
-        <v>120</v>
+      <c r="A34" s="15" t="s">
+        <v>101</v>
       </c>
       <c r="B34" s="2">
         <v>300</v>
@@ -6641,8 +6548,8 @@
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="19" t="s">
-        <v>121</v>
+      <c r="A35" s="14" t="s">
+        <v>102</v>
       </c>
       <c r="B35" s="2">
         <v>300</v>
@@ -6655,8 +6562,8 @@
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="20" t="s">
-        <v>122</v>
+      <c r="A36" s="15" t="s">
+        <v>103</v>
       </c>
       <c r="B36" s="2">
         <v>300</v>
@@ -6669,8 +6576,8 @@
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="19" t="s">
-        <v>123</v>
+      <c r="A37" s="14" t="s">
+        <v>104</v>
       </c>
       <c r="B37" s="2">
         <v>300</v>
@@ -6683,8 +6590,8 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="20" t="s">
-        <v>124</v>
+      <c r="A38" s="15" t="s">
+        <v>105</v>
       </c>
       <c r="B38" s="2">
         <v>300</v>
@@ -6697,8 +6604,8 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="19" t="s">
-        <v>125</v>
+      <c r="A39" s="14" t="s">
+        <v>106</v>
       </c>
       <c r="B39" s="2">
         <v>300</v>
@@ -6711,8 +6618,8 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="20" t="s">
-        <v>126</v>
+      <c r="A40" s="15" t="s">
+        <v>107</v>
       </c>
       <c r="B40" s="2">
         <v>300</v>
@@ -6725,8 +6632,8 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="19" t="s">
-        <v>127</v>
+      <c r="A41" s="14" t="s">
+        <v>108</v>
       </c>
       <c r="B41" s="2">
         <v>300</v>
@@ -6739,8 +6646,8 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="20" t="s">
-        <v>128</v>
+      <c r="A42" s="15" t="s">
+        <v>109</v>
       </c>
       <c r="B42" s="2">
         <v>300</v>
@@ -6753,8 +6660,8 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="19" t="s">
-        <v>129</v>
+      <c r="A43" s="14" t="s">
+        <v>110</v>
       </c>
       <c r="B43" s="2">
         <v>300</v>
@@ -6767,8 +6674,8 @@
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="20" t="s">
-        <v>130</v>
+      <c r="A44" s="15" t="s">
+        <v>111</v>
       </c>
       <c r="B44" s="2">
         <v>300</v>
@@ -6781,8 +6688,8 @@
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="19" t="s">
-        <v>131</v>
+      <c r="A45" s="14" t="s">
+        <v>112</v>
       </c>
       <c r="B45" s="2">
         <v>300</v>
@@ -6795,8 +6702,8 @@
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="20" t="s">
-        <v>132</v>
+      <c r="A46" s="15" t="s">
+        <v>113</v>
       </c>
       <c r="B46" s="2">
         <v>300</v>
@@ -6809,8 +6716,8 @@
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="19" t="s">
-        <v>133</v>
+      <c r="A47" s="14" t="s">
+        <v>114</v>
       </c>
       <c r="B47" s="2">
         <v>300</v>
@@ -6823,8 +6730,8 @@
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="20" t="s">
-        <v>134</v>
+      <c r="A48" s="15" t="s">
+        <v>115</v>
       </c>
       <c r="B48" s="2">
         <v>300</v>
@@ -6837,8 +6744,8 @@
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="19" t="s">
-        <v>135</v>
+      <c r="A49" s="14" t="s">
+        <v>116</v>
       </c>
       <c r="B49" s="2">
         <v>300</v>
@@ -6851,8 +6758,8 @@
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="20" t="s">
-        <v>136</v>
+      <c r="A50" s="15" t="s">
+        <v>117</v>
       </c>
       <c r="B50" s="2">
         <v>300</v>
@@ -6865,8 +6772,8 @@
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="19" t="s">
-        <v>137</v>
+      <c r="A51" s="14" t="s">
+        <v>118</v>
       </c>
       <c r="B51" s="2">
         <v>300</v>
@@ -6879,8 +6786,8 @@
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="20" t="s">
-        <v>138</v>
+      <c r="A52" s="15" t="s">
+        <v>119</v>
       </c>
       <c r="B52" s="2">
         <v>300</v>
@@ -6893,8 +6800,8 @@
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="19" t="s">
-        <v>139</v>
+      <c r="A53" s="14" t="s">
+        <v>120</v>
       </c>
       <c r="B53" s="2">
         <v>300</v>
@@ -6907,8 +6814,8 @@
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="20" t="s">
-        <v>140</v>
+      <c r="A54" s="15" t="s">
+        <v>121</v>
       </c>
       <c r="B54" s="2">
         <v>300</v>
@@ -6921,8 +6828,8 @@
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="19" t="s">
-        <v>141</v>
+      <c r="A55" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B55" s="2">
         <v>300</v>
@@ -6935,8 +6842,8 @@
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="20" t="s">
-        <v>142</v>
+      <c r="A56" s="15" t="s">
+        <v>123</v>
       </c>
       <c r="B56" s="2">
         <v>300</v>
@@ -6949,8 +6856,8 @@
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="19" t="s">
-        <v>143</v>
+      <c r="A57" s="14" t="s">
+        <v>124</v>
       </c>
       <c r="B57" s="2">
         <v>300</v>
@@ -6963,8 +6870,8 @@
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="20" t="s">
-        <v>144</v>
+      <c r="A58" s="15" t="s">
+        <v>125</v>
       </c>
       <c r="B58" s="2">
         <v>300</v>
@@ -6977,8 +6884,8 @@
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="19" t="s">
-        <v>145</v>
+      <c r="A59" s="14" t="s">
+        <v>126</v>
       </c>
       <c r="B59" s="2">
         <v>300</v>
@@ -6991,8 +6898,8 @@
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="20" t="s">
-        <v>146</v>
+      <c r="A60" s="15" t="s">
+        <v>127</v>
       </c>
       <c r="B60" s="2">
         <v>300</v>
@@ -7005,8 +6912,8 @@
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="19" t="s">
-        <v>147</v>
+      <c r="A61" s="14" t="s">
+        <v>128</v>
       </c>
       <c r="B61" s="2">
         <v>300</v>
@@ -7019,8 +6926,8 @@
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="20" t="s">
-        <v>148</v>
+      <c r="A62" s="15" t="s">
+        <v>129</v>
       </c>
       <c r="B62" s="2">
         <v>300</v>
@@ -7033,8 +6940,8 @@
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="19" t="s">
-        <v>149</v>
+      <c r="A63" s="14" t="s">
+        <v>130</v>
       </c>
       <c r="B63" s="2">
         <v>300</v>
@@ -7047,8 +6954,8 @@
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" s="20" t="s">
-        <v>150</v>
+      <c r="A64" s="15" t="s">
+        <v>131</v>
       </c>
       <c r="B64" s="2">
         <v>300</v>
@@ -7061,8 +6968,8 @@
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" s="21" t="s">
-        <v>151</v>
+      <c r="A65" s="16" t="s">
+        <v>132</v>
       </c>
       <c r="B65" s="2">
         <v>300</v>
@@ -7097,131 +7004,131 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
+      <c r="A1" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
     </row>
     <row r="2" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="26" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="B3" s="2">
         <v>4500</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="B4" s="3">
         <v>2100</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="B5" s="2">
         <v>450</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="39" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="26" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="26" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="B9" s="2">
         <v>5</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="26" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="B10" s="3">
         <v>3</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="26" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>98</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="26" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="B12" s="3">
         <v>50</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
